--- a/Data_Table/쥐 성장 테이블.xlsx
+++ b/Data_Table/쥐 성장 테이블.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Growth_Node" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Growth_Order" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Action_Awaken" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Growth_Effect_Type" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth_Node" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth_Order" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action_Awaken" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth_Effect_Type" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -937,6 +937,44 @@
         <v>1.5</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>필살기 해금</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>ultUnlock</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Unlock</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -948,7 +986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1023,7 +1061,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>0</v>
@@ -1034,7 +1072,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>0</v>
@@ -1045,7 +1083,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>0</v>
@@ -1056,7 +1094,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1" t="n">
         <v>0</v>
@@ -1067,7 +1105,7 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C9" s="1" t="n">
         <v>0</v>
@@ -1078,7 +1116,7 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C10" s="1" t="n">
         <v>0</v>
@@ -1089,7 +1127,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1" t="n">
         <v>0</v>
@@ -1100,7 +1138,7 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1" t="n">
         <v>0</v>
@@ -1111,7 +1149,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C13" s="1" t="n">
         <v>0</v>
@@ -1122,7 +1160,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C14" s="1" t="n">
         <v>0</v>
@@ -1133,7 +1171,7 @@
         <v>12</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C15" s="1" t="n">
         <v>0</v>
@@ -1144,7 +1182,7 @@
         <v>13</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1" t="n">
         <v>0</v>
@@ -1199,7 +1237,7 @@
         <v>18</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C21" s="1" t="n">
         <v>0</v>
@@ -1210,7 +1248,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C22" s="1" t="n">
         <v>0</v>
@@ -1232,7 +1270,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C24" s="1" t="n">
         <v>0</v>
@@ -1243,7 +1281,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C25" s="1" t="n">
         <v>0</v>
@@ -1254,10 +1292,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1265,10 +1303,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1276,10 +1314,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1287,7 +1325,7 @@
         <v>26</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C29" s="1" t="n">
         <v>1</v>
@@ -1298,7 +1336,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" s="1" t="n">
         <v>1</v>
@@ -1309,7 +1347,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C31" s="1" t="n">
         <v>1</v>
@@ -1320,9 +1358,42 @@
         <v>29</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C32" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1796,7 +1867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2130,6 +2201,33 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Ult_Unlock</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>필살기 해금 (필살기가 있는 종만). 찍히기 전엔 필살기 게이지가 안 참</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data_Table/쥐 성장 테이블.xlsx
+++ b/Data_Table/쥐 성장 테이블.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -437,6 +437,8 @@
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,6 +492,26 @@
           <t>밸류_03</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>아이콘</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>설명 (화면, {v1}~{v3} 값 · {p1}~{p3} 값×100)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>칸 x (트리 창)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>칸 y</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -542,6 +564,26 @@
           <t>value_03</t>
         </is>
       </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>node_icon</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>node_desc</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>pos_x</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>pos_y</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -594,6 +636,26 @@
           <t>float</t>
         </is>
       </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -630,6 +692,22 @@
         <v>0</v>
       </c>
       <c r="J4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>SkillIcons/cs_teeth</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>이 종의 갉는 힘 ×{v1} (레벨마다 곱해짐)</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -670,6 +748,22 @@
       <c r="J5" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>SkillIcons/cs_speed</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>돌진 속도 +{p1}% (레벨마다)</t>
+        </is>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -708,6 +802,22 @@
       <c r="J6" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t>@action</t>
+        </is>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
+        <is>
+          <t>특수 액션 해금. 2레벨부터 발동 확률·빈도 +{p1}%씩</t>
+        </is>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -746,6 +856,22 @@
       <c r="J7" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="K7" s="1" t="inlineStr">
+        <is>
+          <t>SkillIcons/cs_flip</t>
+        </is>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
+        <is>
+          <t>묘기 확률 +{p1}% (레벨마다)</t>
+        </is>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -784,6 +910,22 @@
       <c r="J8" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="K8" s="1" t="inlineStr">
+        <is>
+          <t>SkillIcons/cs_critc</t>
+        </is>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
+        <is>
+          <t>크리티컬 확률 +{p1}% (레벨마다)</t>
+        </is>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -822,6 +964,22 @@
       <c r="J9" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="K9" s="1" t="inlineStr">
+        <is>
+          <t>@action</t>
+        </is>
+      </c>
+      <c r="L9" s="1" t="inlineStr">
+        <is>
+          <t>특수 액션 위력 +{p1}% (레벨마다)</t>
+        </is>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -860,6 +1018,22 @@
       <c r="J10" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="K10" s="1" t="inlineStr">
+        <is>
+          <t>@passive</t>
+        </is>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
+        <is>
+          <t>특수 능력 세기 +{p1}% (레벨마다)</t>
+        </is>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -898,6 +1072,22 @@
       <c r="J11" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="K11" s="1" t="inlineStr">
+        <is>
+          <t>@action</t>
+        </is>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
+        <is>
+          <t>특수 액션 각성: 액션이 한 단계 더 화려하고 강해짐</t>
+        </is>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -936,6 +1126,22 @@
       <c r="J12" s="1" t="n">
         <v>1.5</v>
       </c>
+      <c r="K12" s="1" t="inlineStr">
+        <is>
+          <t>SkillIcons/cs_core</t>
+        </is>
+      </c>
+      <c r="L12" s="1" t="inlineStr">
+        <is>
+          <t>각성: 갉는 힘 ×{v1} · 특수 능력 ×{v2} · 특수 액션 ×{v3}, 몸에서 빛이 남</t>
+        </is>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -973,6 +1179,22 @@
       </c>
       <c r="J13" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="K13" s="1" t="inlineStr">
+        <is>
+          <t>@ult</t>
+        </is>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
+        <is>
+          <t>필살기 해금: 필살기 게이지가 차기 시작</t>
+        </is>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Table/쥐 성장 테이블.xlsx
+++ b/Data_Table/쥐 성장 테이블.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -439,6 +439,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,60 +455,70 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>노드 이름 키</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>코드 id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>최대 레벨</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>선행 노드</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>선행 레벨</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>효과 타입</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>밸류_01</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>밸류_02</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>밸류_03</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>아이콘</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>설명 (화면, {v1}~{v3} 값 · {p1}~{p3} 값×100)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>설명 (화면, {v1}~{v3} 값 · {p1}~{p3} 값×100) 키</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>칸 x (트리 창)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>칸 y</t>
         </is>
@@ -526,60 +537,70 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
+          <t>node_name_sk</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t>code_id</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>max_level</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>req_node</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>req_level</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>effect_type</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>value_01</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>value_02</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>value_03</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>node_icon</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>node_desc</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>node_desc_sk</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>pos_x</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>pos_y</t>
         </is>
@@ -598,60 +619,70 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>enum</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="N3" s="1" t="inlineStr">
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -666,48 +697,54 @@
           <t>갉기 훈련</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="2" t="n">
+        <v>1900001</v>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>dmg</t>
         </is>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="E4" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="F4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="G4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>Atk_Growth</t>
         </is>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="I4" s="1" t="n">
         <v>1.25</v>
       </c>
-      <c r="I4" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="1" t="inlineStr">
+      <c r="K4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
         <is>
           <t>SkillIcons/cs_teeth</t>
         </is>
       </c>
-      <c r="L4" s="1" t="inlineStr">
+      <c r="M4" s="1" t="inlineStr">
         <is>
           <t>이 종의 갉는 힘 ×{v1} (레벨마다 곱해짐)</t>
         </is>
       </c>
-      <c r="M4" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="N4" s="1" t="n">
+        <v>2000001</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -720,48 +757,54 @@
           <t>뒷발 근육</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="2" t="n">
+        <v>1900002</v>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>legs</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="E5" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="F5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>Dash_Speed_Growth</t>
         </is>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="I5" s="1" t="n">
         <v>0.08</v>
       </c>
-      <c r="I5" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="1" t="inlineStr">
+      <c r="K5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
         <is>
           <t>SkillIcons/cs_speed</t>
         </is>
       </c>
-      <c r="L5" s="1" t="inlineStr">
+      <c r="M5" s="1" t="inlineStr">
         <is>
           <t>돌진 속도 +{p1}% (레벨마다)</t>
         </is>
       </c>
-      <c r="M5" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" s="1" t="n">
+        <v>2000002</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -774,48 +817,54 @@
           <t>특수 액션</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="2" t="n">
+        <v>1900003</v>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>act</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="E6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="F6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="1" t="inlineStr">
+      <c r="G6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
         <is>
           <t>Action_Unlock</t>
         </is>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="I6" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="I6" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="1" t="inlineStr">
+      <c r="K6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="inlineStr">
         <is>
           <t>@action</t>
         </is>
       </c>
-      <c r="L6" s="1" t="inlineStr">
+      <c r="M6" s="1" t="inlineStr">
         <is>
           <t>특수 액션 해금. 2레벨부터 발동 확률·빈도 +{p1}%씩</t>
         </is>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="N6" s="1" t="n">
+        <v>2000003</v>
+      </c>
+      <c r="O6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="N6" s="1" t="n">
+      <c r="P6" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -828,48 +877,54 @@
           <t>재롱 본능</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="2" t="n">
+        <v>1900004</v>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>show</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="E7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="F7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G7" s="1" t="inlineStr">
+      <c r="H7" s="1" t="inlineStr">
         <is>
           <t>Trick_Chance_Growth</t>
         </is>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="I7" s="1" t="n">
         <v>0.4</v>
       </c>
-      <c r="I7" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="1" t="inlineStr">
+      <c r="K7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="inlineStr">
         <is>
           <t>SkillIcons/cs_flip</t>
         </is>
       </c>
-      <c r="L7" s="1" t="inlineStr">
+      <c r="M7" s="1" t="inlineStr">
         <is>
           <t>묘기 확률 +{p1}% (레벨마다)</t>
         </is>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="N7" s="1" t="n">
+        <v>2000004</v>
+      </c>
+      <c r="O7" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="N7" s="1" t="n">
+      <c r="P7" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -882,48 +937,54 @@
           <t>급소 갉기</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="2" t="n">
+        <v>1900005</v>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>crit</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="E8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="F8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="G8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="1" t="inlineStr">
+      <c r="H8" s="1" t="inlineStr">
         <is>
           <t>Crit_Chance_Growth</t>
         </is>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="I8" s="1" t="n">
         <v>0.04</v>
       </c>
-      <c r="I8" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="1" t="inlineStr">
+      <c r="K8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="inlineStr">
         <is>
           <t>SkillIcons/cs_critc</t>
         </is>
       </c>
-      <c r="L8" s="1" t="inlineStr">
+      <c r="M8" s="1" t="inlineStr">
         <is>
           <t>크리티컬 확률 +{p1}% (레벨마다)</t>
         </is>
       </c>
-      <c r="M8" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" s="1" t="n">
+        <v>2000005</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1" t="n">
         <v>2</v>
       </c>
     </row>
@@ -936,48 +997,54 @@
           <t>액션 위력</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="2" t="n">
+        <v>1900006</v>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>actPow</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="E9" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="F9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="G9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
         <is>
           <t>Action_Power_Growth</t>
         </is>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="I9" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="I9" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K9" s="1" t="inlineStr">
+      <c r="K9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1" t="inlineStr">
         <is>
           <t>@action</t>
         </is>
       </c>
-      <c r="L9" s="1" t="inlineStr">
+      <c r="M9" s="1" t="inlineStr">
         <is>
           <t>특수 액션 위력 +{p1}% (레벨마다)</t>
         </is>
       </c>
-      <c r="M9" s="1" t="n">
+      <c r="N9" s="1" t="n">
+        <v>2000006</v>
+      </c>
+      <c r="O9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="N9" s="1" t="n">
+      <c r="P9" s="1" t="n">
         <v>2</v>
       </c>
     </row>
@@ -990,48 +1057,54 @@
           <t>특수 강화</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C10" s="2" t="n">
+        <v>1900007</v>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>special</t>
         </is>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="E10" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="1" t="n">
+      <c r="F10" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="1" t="n">
+      <c r="G10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>Passive_Power_Growth</t>
         </is>
       </c>
-      <c r="H10" s="1" t="n">
+      <c r="I10" s="1" t="n">
         <v>0.35</v>
       </c>
-      <c r="I10" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="1" t="inlineStr">
+      <c r="K10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1" t="inlineStr">
         <is>
           <t>@passive</t>
         </is>
       </c>
-      <c r="L10" s="1" t="inlineStr">
+      <c r="M10" s="1" t="inlineStr">
         <is>
           <t>특수 능력 세기 +{p1}% (레벨마다)</t>
         </is>
       </c>
-      <c r="M10" s="1" t="n">
+      <c r="N10" s="1" t="n">
+        <v>2000007</v>
+      </c>
+      <c r="O10" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="N10" s="1" t="n">
+      <c r="P10" s="1" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1044,48 +1117,54 @@
           <t>액션 각성</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C11" s="2" t="n">
+        <v>1900008</v>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>actX</t>
         </is>
       </c>
-      <c r="D11" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="E11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="G11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>Action_Awaken</t>
         </is>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="1" t="inlineStr">
+      <c r="K11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="inlineStr">
         <is>
           <t>@action</t>
         </is>
       </c>
-      <c r="L11" s="1" t="inlineStr">
+      <c r="M11" s="1" t="inlineStr">
         <is>
           <t>특수 액션 각성: 액션이 한 단계 더 화려하고 강해짐</t>
         </is>
       </c>
-      <c r="M11" s="1" t="n">
+      <c r="N11" s="1" t="n">
+        <v>2000008</v>
+      </c>
+      <c r="O11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="N11" s="1" t="n">
+      <c r="P11" s="1" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1098,48 +1177,54 @@
           <t>각성</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C12" s="2" t="n">
+        <v>1900009</v>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>ult</t>
         </is>
       </c>
-      <c r="D12" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="E12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="F12" s="1" t="n">
+      <c r="G12" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>Awaken</t>
         </is>
       </c>
-      <c r="H12" s="1" t="n">
+      <c r="I12" s="1" t="n">
         <v>3</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>1.5</v>
       </c>
       <c r="J12" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="K12" s="1" t="inlineStr">
+      <c r="K12" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L12" s="1" t="inlineStr">
         <is>
           <t>SkillIcons/cs_core</t>
         </is>
       </c>
-      <c r="L12" s="1" t="inlineStr">
+      <c r="M12" s="1" t="inlineStr">
         <is>
           <t>각성: 갉는 힘 ×{v1} · 특수 능력 ×{v2} · 특수 액션 ×{v3}, 몸에서 빛이 남</t>
         </is>
       </c>
-      <c r="M12" s="1" t="n">
+      <c r="N12" s="1" t="n">
+        <v>2000009</v>
+      </c>
+      <c r="O12" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="N12" s="1" t="n">
+      <c r="P12" s="1" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1152,48 +1237,54 @@
           <t>필살기 해금</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C13" s="2" t="n">
+        <v>1900010</v>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
         <is>
           <t>ultUnlock</t>
         </is>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="E13" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="G13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>Ult_Unlock</t>
         </is>
       </c>
-      <c r="H13" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="I13" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K13" s="1" t="inlineStr">
+      <c r="K13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1" t="inlineStr">
         <is>
           <t>@ult</t>
         </is>
       </c>
-      <c r="L13" s="1" t="inlineStr">
+      <c r="M13" s="1" t="inlineStr">
         <is>
           <t>필살기 해금: 필살기 게이지가 차기 시작</t>
         </is>
       </c>
-      <c r="M13" s="1" t="n">
-        <v>1</v>
-      </c>
       <c r="N13" s="1" t="n">
+        <v>2000010</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1" t="n">
         <v>1</v>
       </c>
     </row>

--- a/Data_Table/쥐 성장 테이블.xlsx
+++ b/Data_Table/쥐 성장 테이블.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Growth_Node" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Growth_Order" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Action_Awaken" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Growth_Effect_Type" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth_Node" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth_Order" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action_Awaken" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth_Effect_Type" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
